--- a/course-design-2/outputs/tables/ch7/49_stage26_3_metrics_after_feature_removal.xlsx
+++ b/course-design-2/outputs/tables/ch7/49_stage26_3_metrics_after_feature_removal.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_特征组维度对照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_三种划分统一协议" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_消融五配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_消融增量bootstrap" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_模型比较" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_最终模型测试集" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_分组预测误差四分位" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位大类预测误差" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_多种子明细" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_多种子汇总" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司分组多次划分" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_公司分组汇总" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_稳健性对照" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_主模型SHAP特征" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_技能SHAP" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="01_特征组维度对照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_三种划分统一协议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_消融五配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_消融增量bootstrap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_模型比较" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_最终模型测试集" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_分组预测误差四分位" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_岗位大类预测误差" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_多种子明细" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_多种子汇总" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_公司分组多次划分" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_公司分组汇总" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_稳健性对照" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_主模型SHAP特征" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_技能SHAP" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.470458</v>
+        <v>36.505337</v>
       </c>
       <c r="C2" t="n">
-        <v>1.288387</v>
+        <v>1.189704</v>
       </c>
       <c r="D2" t="n">
-        <v>36.311997</v>
+        <v>36.236393</v>
       </c>
       <c r="E2" t="n">
-        <v>0.272973</v>
+        <v>0.36827</v>
       </c>
     </row>
     <row r="3">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.795565</v>
+        <v>35.797968</v>
       </c>
       <c r="C3" t="n">
-        <v>1.293429</v>
+        <v>1.273845</v>
       </c>
       <c r="D3" t="n">
-        <v>35.611477</v>
+        <v>35.652079</v>
       </c>
       <c r="E3" t="n">
-        <v>0.789422</v>
+        <v>0.725893</v>
       </c>
     </row>
   </sheetData>
@@ -814,13 +814,13 @@
         <v>1688</v>
       </c>
       <c r="G2" t="n">
-        <v>52.093534</v>
+        <v>51.629921</v>
       </c>
       <c r="H2" t="n">
-        <v>103.691486</v>
+        <v>103.613495</v>
       </c>
       <c r="I2" t="n">
-        <v>0.133895</v>
+        <v>0.135197</v>
       </c>
     </row>
     <row r="3">
@@ -843,13 +843,13 @@
         <v>2842</v>
       </c>
       <c r="G3" t="n">
-        <v>82.47614900000001</v>
+        <v>82.58488</v>
       </c>
       <c r="H3" t="n">
-        <v>123.390683</v>
+        <v>123.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.011671</v>
+        <v>-0.008298</v>
       </c>
     </row>
     <row r="4">
@@ -872,13 +872,13 @@
         <v>1988</v>
       </c>
       <c r="G4" t="n">
-        <v>39.044977</v>
+        <v>38.900334</v>
       </c>
       <c r="H4" t="n">
-        <v>62.179762</v>
+        <v>61.7547</v>
       </c>
       <c r="I4" t="n">
-        <v>0.144406</v>
+        <v>0.156064</v>
       </c>
     </row>
     <row r="5">
@@ -901,13 +901,13 @@
         <v>1867</v>
       </c>
       <c r="G5" t="n">
-        <v>49.309929</v>
+        <v>50.045322</v>
       </c>
       <c r="H5" t="n">
-        <v>101.15176</v>
+        <v>103.444926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.126647</v>
+        <v>0.086599</v>
       </c>
     </row>
     <row r="6">
@@ -930,13 +930,13 @@
         <v>1870</v>
       </c>
       <c r="G6" t="n">
-        <v>47.308772</v>
+        <v>47.035979</v>
       </c>
       <c r="H6" t="n">
-        <v>80.328197</v>
+        <v>80.35033</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07296800000000001</v>
+        <v>0.07245699999999999</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.046672</v>
+        <v>54.039287</v>
       </c>
     </row>
     <row r="3">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.620295</v>
+        <v>16.694624</v>
       </c>
     </row>
     <row r="4">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.044977</v>
+        <v>38.900334</v>
       </c>
     </row>
     <row r="5">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.47614900000001</v>
+        <v>82.58488</v>
       </c>
     </row>
     <row r="6">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94.14837799999999</v>
+        <v>94.46965</v>
       </c>
     </row>
     <row r="7">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.495853</v>
+        <v>23.761042</v>
       </c>
     </row>
     <row r="8">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.093249</v>
+        <v>0.088404</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.064815</v>
+        <v>0.063985</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>真实薪资，主口径未缩尾</t>
+          <t>真实薪资，主统计范围未缩尾</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="D2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.938834</v>
+        <v>34.626154</v>
       </c>
       <c r="D3" t="n">
-        <v>67.93594</v>
+        <v>67.781775</v>
       </c>
       <c r="E3" t="n">
-        <v>0.54093</v>
+        <v>0.543011</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>目标口径 薪资下限</t>
+          <t>目标定义 薪资下限</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.609474</v>
+        <v>40.615346</v>
       </c>
       <c r="D4" t="n">
-        <v>73.84469799999999</v>
+        <v>73.904258</v>
       </c>
       <c r="E4" t="n">
-        <v>0.457601</v>
+        <v>0.456726</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>目标口径 薪资上限</t>
+          <t>目标定义 薪资上限</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.608849</v>
+        <v>48.320296</v>
       </c>
       <c r="D5" t="n">
-        <v>74.051376</v>
+        <v>74.64457</v>
       </c>
       <c r="E5" t="n">
-        <v>0.454561</v>
+        <v>0.445787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.958010，共有特征 308 个</t>
+          <t>0.955780，共有特征 308 个</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.924430；0.885505（共同特征 308 个）</t>
+          <t>0.921362；0.883417（共同特征 308 个）</t>
         </is>
       </c>
     </row>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.650814</v>
+        <v>14.705638</v>
       </c>
       <c r="C2" t="n">
-        <v>0.092483</v>
+        <v>0.092603</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>142.205072</v>
+        <v>143.303137</v>
       </c>
     </row>
     <row r="3">
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.135123</v>
+        <v>7.330178</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04504</v>
+        <v>0.046159</v>
       </c>
       <c r="D3" t="n">
         <v>882</v>
       </c>
       <c r="E3" t="n">
-        <v>7.761496</v>
+        <v>7.462976</v>
       </c>
     </row>
     <row r="4">
@@ -1321,16 +1321,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.850328</v>
+        <v>6.177796</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03693</v>
+        <v>0.038902</v>
       </c>
       <c r="D4" t="n">
         <v>1091</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.324489</v>
+        <v>-5.444624</v>
       </c>
     </row>
     <row r="5">
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.477707</v>
+        <v>5.81999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.034578</v>
+        <v>0.036649</v>
       </c>
       <c r="D5" t="n">
         <v>2085</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.045766</v>
+        <v>-0.9770219999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.768654</v>
+        <v>5.210702</v>
       </c>
       <c r="C6" t="n">
-        <v>0.030102</v>
+        <v>0.032813</v>
       </c>
       <c r="D6" t="n">
         <v>1374</v>
       </c>
       <c r="E6" t="n">
-        <v>3.979958</v>
+        <v>4.299848</v>
       </c>
     </row>
     <row r="7">
@@ -1378,73 +1378,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.528253</v>
+        <v>4.677698</v>
       </c>
       <c r="C7" t="n">
-        <v>0.028585</v>
+        <v>0.029456</v>
       </c>
       <c r="D7" t="n">
         <v>1539</v>
       </c>
       <c r="E7" t="n">
-        <v>3.421217</v>
+        <v>3.572391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>文本SVD4</t>
+          <t>岗位细分类集合=人工智能</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.043529</v>
+        <v>4.118153</v>
       </c>
       <c r="C8" t="n">
-        <v>0.025525</v>
+        <v>0.025933</v>
       </c>
       <c r="D8" t="n">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="E8" t="n">
-        <v>4.648573</v>
+        <v>19.641069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>学历等级</t>
+          <t>文本SVD4</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.824677</v>
+        <v>4.048801</v>
       </c>
       <c r="C9" t="n">
-        <v>0.024143</v>
+        <v>0.025496</v>
       </c>
       <c r="D9" t="n">
-        <v>1934</v>
+        <v>969</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.698518</v>
+        <v>4.675362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>岗位细分类集合=人工智能</t>
+          <t>学历等级</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.80716</v>
+        <v>3.731974</v>
       </c>
       <c r="C10" t="n">
-        <v>0.024033</v>
+        <v>0.023501</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>1934</v>
       </c>
       <c r="E10" t="n">
-        <v>17.60929</v>
+        <v>-0.693551</v>
       </c>
     </row>
     <row r="11">
@@ -1454,16 +1454,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.704116</v>
+        <v>3.707983</v>
       </c>
       <c r="C11" t="n">
-        <v>0.023382</v>
+        <v>0.02335</v>
       </c>
       <c r="D11" t="n">
         <v>985</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.503971</v>
+        <v>-3.297125</v>
       </c>
     </row>
     <row r="12">
@@ -1473,16 +1473,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.63502</v>
+        <v>3.639079</v>
       </c>
       <c r="C12" t="n">
-        <v>0.022946</v>
+        <v>0.022916</v>
       </c>
       <c r="D12" t="n">
         <v>1003</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.714797</v>
+        <v>-3.417148</v>
       </c>
     </row>
     <row r="13">
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.383803</v>
+        <v>3.459057</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02136</v>
+        <v>0.021782</v>
       </c>
       <c r="D13" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.143047</v>
+        <v>-3.317593</v>
       </c>
     </row>
     <row r="14">
@@ -1511,16 +1511,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.208004</v>
+        <v>2.945658</v>
       </c>
       <c r="C14" t="n">
-        <v>0.020251</v>
+        <v>0.018549</v>
       </c>
       <c r="D14" t="n">
         <v>1111</v>
       </c>
       <c r="E14" t="n">
-        <v>3.14565</v>
+        <v>2.841705</v>
       </c>
     </row>
     <row r="15">
@@ -1530,35 +1530,35 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.612568</v>
+        <v>2.696593</v>
       </c>
       <c r="C15" t="n">
-        <v>0.016492</v>
+        <v>0.016981</v>
       </c>
       <c r="D15" t="n">
         <v>149</v>
       </c>
       <c r="E15" t="n">
-        <v>19.211357</v>
+        <v>19.806623</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>公司标签列表=节日礼品</t>
+          <t>办公工具技能数</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.377729</v>
+        <v>2.390356</v>
       </c>
       <c r="C16" t="n">
-        <v>0.015009</v>
+        <v>0.015052</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>642</v>
       </c>
       <c r="E16" t="n">
-        <v>22.914475</v>
+        <v>-3.933457</v>
       </c>
     </row>
   </sheetData>
@@ -1615,10 +1615,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>20.309731</v>
+        <v>18.895386</v>
       </c>
       <c r="E2" t="n">
-        <v>1.595466</v>
+        <v>1.544092</v>
       </c>
     </row>
     <row r="3">
@@ -1634,10 +1634,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>39.450919</v>
+        <v>37.063207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.568829</v>
+        <v>0.537763</v>
       </c>
     </row>
     <row r="4">
@@ -1653,10 +1653,10 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.252545</v>
+        <v>-1.397708</v>
       </c>
       <c r="E4" t="n">
-        <v>0.424138</v>
+        <v>0.41965</v>
       </c>
     </row>
     <row r="5">
@@ -1672,29 +1672,29 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>5.613044</v>
+        <v>4.4638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.410317</v>
+        <v>0.323876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>办公软件</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>419</v>
+        <v>2591</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>361</v>
       </c>
       <c r="D6" t="n">
-        <v>6.378203</v>
+        <v>-0.642235</v>
       </c>
       <c r="E6" t="n">
-        <v>0.298474</v>
+        <v>0.287768</v>
       </c>
     </row>
     <row r="7">
@@ -1710,390 +1710,390 @@
         <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.605727</v>
+        <v>-0.684283</v>
       </c>
       <c r="E7" t="n">
-        <v>0.287314</v>
+        <v>0.238274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>办公软件</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2591</v>
+        <v>419</v>
       </c>
       <c r="C8" t="n">
-        <v>361</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.602569</v>
+        <v>4.596505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.27834</v>
+        <v>0.23797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>项目管理</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>619</v>
+        <v>487</v>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.802243</v>
+        <v>3.630267</v>
       </c>
       <c r="E9" t="n">
-        <v>0.244993</v>
+        <v>0.218202</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>深度学习</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>0.185444</v>
+        <v>-2.119757</v>
       </c>
       <c r="E10" t="n">
-        <v>0.192438</v>
+        <v>0.217002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>295</v>
+        <v>179</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>5.033364</v>
+        <v>7.378255</v>
       </c>
       <c r="E11" t="n">
-        <v>0.169483</v>
+        <v>0.159323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>深度学习</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>179</v>
+        <v>572</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>9.070301000000001</v>
+        <v>-1.460794</v>
       </c>
       <c r="E12" t="n">
-        <v>0.164902</v>
+        <v>0.152885</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>项目管理</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>487</v>
+        <v>231</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>2.375569</v>
+        <v>2.401782</v>
       </c>
       <c r="E13" t="n">
-        <v>0.145479</v>
+        <v>0.131006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>1.59028</v>
+        <v>3.160007</v>
       </c>
       <c r="E14" t="n">
-        <v>0.119964</v>
+        <v>0.120394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>大数据</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>3.390473</v>
+        <v>-2.316639</v>
       </c>
       <c r="E15" t="n">
-        <v>0.092444</v>
+        <v>0.104936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>446</v>
+        <v>238</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>1.443804</v>
+        <v>3.352356</v>
       </c>
       <c r="E16" t="n">
-        <v>0.088058</v>
+        <v>0.09164899999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>大模型</t>
+          <t>Prompt Engineering</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>866</v>
+        <v>202</v>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>0.585784</v>
+        <v>-3.165765</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07851900000000001</v>
+        <v>0.087244</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prompt Engineering</t>
+          <t>大模型</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>202</v>
+        <v>866</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.744291</v>
+        <v>0.575404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07831100000000001</v>
+        <v>0.08491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>产品设计</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>484</v>
+        <v>446</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>0.862005</v>
+        <v>1.126344</v>
       </c>
       <c r="E19" t="n">
-        <v>0.061806</v>
+        <v>0.074971</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MATLAB</t>
+          <t>原型设计</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>118</v>
+        <v>445</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="D20" t="n">
-        <v>4.565779</v>
+        <v>1.385965</v>
       </c>
       <c r="E20" t="n">
-        <v>0.061594</v>
+        <v>0.068438</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>MATLAB</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>4.564088</v>
+        <v>3.621004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.055087</v>
+        <v>0.051461</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>原型设计</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>445</v>
+        <v>205</v>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>1.192743</v>
+        <v>2.201653</v>
       </c>
       <c r="E22" t="n">
-        <v>0.052803</v>
+        <v>0.04988</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>2.283927</v>
+        <v>3.145494</v>
       </c>
       <c r="E23" t="n">
-        <v>0.052133</v>
+        <v>0.049464</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>TensorFlow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="C24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>1.702743</v>
+        <v>-1.244522</v>
       </c>
       <c r="E24" t="n">
-        <v>0.050848</v>
+        <v>0.047529</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TensorFlow</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>277</v>
+        <v>2418</v>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>374</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.610609</v>
+        <v>-0.093982</v>
       </c>
       <c r="E25" t="n">
-        <v>0.049511</v>
+        <v>0.045385</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>大数据</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="C26" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.086094</v>
+        <v>1.338755</v>
       </c>
       <c r="E26" t="n">
-        <v>0.042894</v>
+        <v>0.041555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D27" t="n">
-        <v>1.693931</v>
+        <v>-0.961083</v>
       </c>
       <c r="E27" t="n">
-        <v>0.041898</v>
+        <v>0.038997</v>
       </c>
     </row>
     <row r="28">
@@ -2109,422 +2109,422 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>1.960333</v>
+        <v>1.955409</v>
       </c>
       <c r="E28" t="n">
-        <v>0.038642</v>
+        <v>0.036787</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>市场调研</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>437</v>
+        <v>1387</v>
       </c>
       <c r="C29" t="n">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.646269</v>
+        <v>0.176623</v>
       </c>
       <c r="E29" t="n">
-        <v>0.034002</v>
+        <v>0.035982</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>市场调研</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>210</v>
+        <v>437</v>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.512134</v>
+        <v>-0.6566689999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.033688</v>
+        <v>0.035161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AIGC</t>
+          <t>前端</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>313</v>
+        <v>228</v>
       </c>
       <c r="C31" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.354326</v>
+        <v>1.199815</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031923</v>
+        <v>0.03402</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>微调</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>2.080506</v>
+        <v>-1.797368</v>
       </c>
       <c r="E32" t="n">
-        <v>0.026504</v>
+        <v>0.032409</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2418</v>
+        <v>156</v>
       </c>
       <c r="C33" t="n">
-        <v>374</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.027427</v>
+        <v>1.78618</v>
       </c>
       <c r="E33" t="n">
-        <v>0.026144</v>
+        <v>0.031935</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PyTorch</t>
+          <t>AIGC</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="C34" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.11973</v>
+        <v>-0.584211</v>
       </c>
       <c r="E34" t="n">
-        <v>0.016814</v>
+        <v>0.03045</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>PyTorch</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1341</v>
+        <v>394</v>
       </c>
       <c r="C35" t="n">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="D35" t="n">
-        <v>0.064017</v>
+        <v>-0.377143</v>
       </c>
       <c r="E35" t="n">
-        <v>0.015952</v>
+        <v>0.026096</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>152</v>
+        <v>2737</v>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="D36" t="n">
-        <v>0.445503</v>
+        <v>0.078431</v>
       </c>
       <c r="E36" t="n">
-        <v>0.015238</v>
+        <v>0.02578</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>数据挖掘</t>
+          <t>产品设计</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>156</v>
+        <v>484</v>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D37" t="n">
-        <v>0.41228</v>
+        <v>0.355223</v>
       </c>
       <c r="E37" t="n">
-        <v>0.014415</v>
+        <v>0.025218</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>266</v>
+        <v>152</v>
       </c>
       <c r="C38" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03734</v>
+        <v>0.913724</v>
       </c>
       <c r="E38" t="n">
-        <v>0.014397</v>
+        <v>0.024421</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2737</v>
+        <v>210</v>
       </c>
       <c r="C39" t="n">
-        <v>426</v>
+        <v>36</v>
       </c>
       <c r="D39" t="n">
-        <v>0.018826</v>
+        <v>-0.888567</v>
       </c>
       <c r="E39" t="n">
-        <v>0.013646</v>
+        <v>0.022363</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>用户研究</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1387</v>
+        <v>383</v>
       </c>
       <c r="C40" t="n">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="D40" t="n">
-        <v>0.04891</v>
+        <v>0.351346</v>
       </c>
       <c r="E40" t="n">
-        <v>0.012991</v>
+        <v>0.019387</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>数据可视化</t>
+          <t>微调</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>409</v>
+        <v>132</v>
       </c>
       <c r="C41" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>0.240141</v>
+        <v>0.9882339999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.012701</v>
+        <v>0.013472</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>PPT</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>110</v>
+        <v>1341</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.953856</v>
+        <v>0.056657</v>
       </c>
       <c r="E42" t="n">
-        <v>0.011953</v>
+        <v>0.011213</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>内容运营</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>140</v>
+        <v>774</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.693805</v>
+        <v>0.091862</v>
       </c>
       <c r="E43" t="n">
-        <v>0.010172</v>
+        <v>0.009009</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>后端</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>599</v>
+        <v>235</v>
       </c>
       <c r="C44" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D44" t="n">
-        <v>0.107375</v>
+        <v>0.155069</v>
       </c>
       <c r="E44" t="n">
-        <v>0.009016</v>
+        <v>0.006662</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>用户研究</t>
+          <t>数据运营</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>383</v>
+        <v>146</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D45" t="n">
-        <v>0.114805</v>
+        <v>0.330738</v>
       </c>
       <c r="E45" t="n">
-        <v>0.008917</v>
+        <v>0.006451</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.598542</v>
+        <v>-0.100169</v>
       </c>
       <c r="E46" t="n">
-        <v>0.007638</v>
+        <v>0.004119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>后端</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="C47" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D47" t="n">
-        <v>0.124843</v>
+        <v>0.08774800000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.006802</v>
+        <v>0.002464</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>内容运营</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>774</v>
+        <v>143</v>
       </c>
       <c r="C48" t="n">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>0.050326</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>单元测试</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C49" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.309497</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.004452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>165</v>
+        <v>599</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2536,14 +2536,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>单元测试</t>
+          <t>React</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2555,14 +2555,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>数据运营</t>
+          <t>数据可视化</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>146</v>
+        <v>409</v>
       </c>
       <c r="C52" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2669,22 +2669,22 @@
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="H2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="I2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
       <c r="J2" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="K2" t="n">
-        <v>69.870515</v>
+        <v>69.5295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.58968</v>
+        <v>0.593675</v>
       </c>
     </row>
     <row r="3">
@@ -2709,22 +2709,22 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>52.093534</v>
+        <v>51.629921</v>
       </c>
       <c r="H3" t="n">
-        <v>103.691486</v>
+        <v>103.613495</v>
       </c>
       <c r="I3" t="n">
-        <v>0.133895</v>
+        <v>0.135197</v>
       </c>
       <c r="J3" t="n">
-        <v>56.83264</v>
+        <v>56.91992</v>
       </c>
       <c r="K3" t="n">
-        <v>99.962637</v>
+        <v>99.77120600000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14214</v>
+        <v>0.145423</v>
       </c>
     </row>
     <row r="4">
@@ -2749,22 +2749,22 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>32.132572</v>
+        <v>31.858455</v>
       </c>
       <c r="H4" t="n">
-        <v>47.817303</v>
+        <v>48.03658</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6533949999999999</v>
+        <v>0.650209</v>
       </c>
       <c r="J4" t="n">
-        <v>39.289746</v>
+        <v>38.79574</v>
       </c>
       <c r="K4" t="n">
-        <v>72.738175</v>
+        <v>71.836651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.503167</v>
+        <v>0.515406</v>
       </c>
     </row>
   </sheetData>
@@ -2942,22 +2942,22 @@
         <v>246</v>
       </c>
       <c r="D4" t="n">
-        <v>36.684903</v>
+        <v>36.596275</v>
       </c>
       <c r="E4" t="n">
-        <v>70.934708</v>
+        <v>71.288178</v>
       </c>
       <c r="F4" t="n">
-        <v>0.577086</v>
+        <v>0.57286</v>
       </c>
       <c r="G4" t="n">
-        <v>36.163106</v>
+        <v>36.490756</v>
       </c>
       <c r="H4" t="n">
-        <v>66.26462600000001</v>
+        <v>66.761292</v>
       </c>
       <c r="I4" t="n">
-        <v>0.563239</v>
+        <v>0.5566680000000001</v>
       </c>
       <c r="J4" t="n">
         <v>10418</v>
@@ -2984,22 +2984,22 @@
         <v>308</v>
       </c>
       <c r="D5" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="E5" t="n">
-        <v>69.870515</v>
+        <v>69.5295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58968</v>
+        <v>0.593675</v>
       </c>
       <c r="G5" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="H5" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="I5" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
       <c r="J5" t="n">
         <v>10418</v>
@@ -3026,22 +3026,22 @@
         <v>310</v>
       </c>
       <c r="D6" t="n">
-        <v>36.447279</v>
+        <v>36.437977</v>
       </c>
       <c r="E6" t="n">
-        <v>69.70617799999999</v>
+        <v>69.80105399999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.591608</v>
+        <v>0.590495</v>
       </c>
       <c r="G6" t="n">
-        <v>36.310077</v>
+        <v>36.4177</v>
       </c>
       <c r="H6" t="n">
-        <v>66.51470999999999</v>
+        <v>67.38436900000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.559936</v>
+        <v>0.548354</v>
       </c>
       <c r="J6" t="n">
         <v>10418</v>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="E2" t="n">
-        <v>36.447279</v>
+        <v>36.437977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.067375</v>
+        <v>-0.147325</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.419282</v>
+        <v>-0.573821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5450469999999999</v>
+        <v>0.361492</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3168,19 +3168,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="E3" t="n">
-        <v>36.310077</v>
+        <v>36.4177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.141786</v>
+        <v>-0.063206</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.313526</v>
+        <v>-0.497289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.587892</v>
+        <v>0.352418</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3282,16 +3282,16 @@
         <v>36.553562</v>
       </c>
       <c r="E6" t="n">
-        <v>36.684903</v>
+        <v>36.596275</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.131341</v>
+        <v>-0.042713</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.254886</v>
+        <v>-1.26168</v>
       </c>
       <c r="H6" t="n">
-        <v>1.029385</v>
+        <v>1.099438</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3319,16 +3319,16 @@
         <v>34.867155</v>
       </c>
       <c r="E7" t="n">
-        <v>36.163106</v>
+        <v>36.490756</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.295952</v>
+        <v>-1.623601</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.427373</v>
+        <v>-2.711675</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.264999</v>
+        <v>-0.55621</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3356,16 +3356,16 @@
         <v>36.553562</v>
       </c>
       <c r="E8" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="F8" t="n">
-        <v>0.038909</v>
+        <v>0.262911</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.241114</v>
+        <v>-0.953264</v>
       </c>
       <c r="H8" t="n">
-        <v>1.323666</v>
+        <v>1.581866</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
         <v>34.867155</v>
       </c>
       <c r="E9" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.584708</v>
+        <v>-1.487339</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.711612</v>
+        <v>-2.61116</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.461833</v>
+        <v>-0.374832</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3478,22 +3478,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="D2" t="n">
-        <v>69.870515</v>
+        <v>69.5295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58968</v>
+        <v>0.593675</v>
       </c>
       <c r="F2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="G2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
     </row>
     <row r="3">
@@ -3508,22 +3508,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.688228</v>
+        <v>36.672834</v>
       </c>
       <c r="D3" t="n">
-        <v>69.111553</v>
+        <v>68.519842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.598546</v>
+        <v>0.60539</v>
       </c>
       <c r="F3" t="n">
-        <v>36.462146</v>
+        <v>36.281077</v>
       </c>
       <c r="G3" t="n">
-        <v>65.00704899999999</v>
+        <v>64.754706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.57966</v>
+        <v>0.582917</v>
       </c>
     </row>
     <row r="4">
@@ -3538,22 +3538,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.221277</v>
+        <v>37.973974</v>
       </c>
       <c r="D4" t="n">
-        <v>74.38752700000001</v>
+        <v>73.779841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5349120000000001</v>
+        <v>0.54248</v>
       </c>
       <c r="F4" t="n">
-        <v>37.045813</v>
+        <v>36.918553</v>
       </c>
       <c r="G4" t="n">
-        <v>68.81978100000001</v>
+        <v>69.247167</v>
       </c>
       <c r="H4" t="n">
-        <v>0.528907</v>
+        <v>0.523038</v>
       </c>
     </row>
     <row r="5">
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.315019</v>
+        <v>45.314378</v>
       </c>
       <c r="D5" t="n">
-        <v>85.583927</v>
+        <v>85.582283</v>
       </c>
       <c r="E5" t="n">
-        <v>0.384371</v>
+        <v>0.384394</v>
       </c>
       <c r="F5" t="n">
-        <v>43.673798</v>
+        <v>43.674895</v>
       </c>
       <c r="G5" t="n">
-        <v>77.239881</v>
+        <v>77.24099</v>
       </c>
       <c r="H5" t="n">
-        <v>0.406579</v>
+        <v>0.406562</v>
       </c>
     </row>
     <row r="6">
@@ -3699,13 +3699,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="C2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="D2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.28104</v>
+        <v>35.109171</v>
       </c>
       <c r="C3" t="n">
-        <v>64.783455</v>
+        <v>64.616632</v>
       </c>
       <c r="D3" t="n">
-        <v>0.582546</v>
+        <v>0.584694</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -3792,10 +3792,10 @@
         <v>2233</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28104</v>
+        <v>35.109171</v>
       </c>
       <c r="E2" t="n">
-        <v>64.783455</v>
+        <v>64.616632</v>
       </c>
     </row>
     <row r="3">
@@ -3813,10 +3813,10 @@
         <v>628</v>
       </c>
       <c r="D3" t="n">
-        <v>35.434828</v>
+        <v>35.821356</v>
       </c>
       <c r="E3" t="n">
-        <v>48.986959</v>
+        <v>49.961485</v>
       </c>
     </row>
     <row r="4">
@@ -3834,10 +3834,10 @@
         <v>702</v>
       </c>
       <c r="D4" t="n">
-        <v>22.679834</v>
+        <v>22.326196</v>
       </c>
       <c r="E4" t="n">
-        <v>32.165038</v>
+        <v>30.765701</v>
       </c>
     </row>
     <row r="5">
@@ -3855,10 +3855,10 @@
         <v>477</v>
       </c>
       <c r="D5" t="n">
-        <v>29.330488</v>
+        <v>28.93682</v>
       </c>
       <c r="E5" t="n">
-        <v>40.764663</v>
+        <v>39.968253</v>
       </c>
     </row>
     <row r="6">
@@ -3876,10 +3876,10 @@
         <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>62.482639</v>
+        <v>62.035479</v>
       </c>
       <c r="E6" t="n">
-        <v>122.049236</v>
+        <v>121.892655</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3928,10 @@
         <v>933</v>
       </c>
       <c r="C2" t="n">
-        <v>29.295129</v>
+        <v>29.396959</v>
       </c>
       <c r="D2" t="n">
-        <v>43.609982</v>
+        <v>43.730844</v>
       </c>
     </row>
     <row r="3">
@@ -3944,58 +3944,58 @@
         <v>1493</v>
       </c>
       <c r="C3" t="n">
-        <v>29.502945</v>
+        <v>29.39985</v>
       </c>
       <c r="D3" t="n">
-        <v>43.547086</v>
+        <v>43.294897</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>技术管理</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>31.943268</v>
+        <v>32.971489</v>
       </c>
       <c r="D4" t="n">
-        <v>41.119023</v>
+        <v>44.98865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>技术管理</t>
+          <t>客服</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="C5" t="n">
-        <v>32.274806</v>
+        <v>33.069425</v>
       </c>
       <c r="D5" t="n">
-        <v>45.22604</v>
+        <v>58.25892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>客服</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="C6" t="n">
-        <v>33.447434</v>
+        <v>33.269944</v>
       </c>
       <c r="D6" t="n">
-        <v>58.779362</v>
+        <v>43.399957</v>
       </c>
     </row>
     <row r="7">
@@ -4008,10 +4008,10 @@
         <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>48.667314</v>
+        <v>48.949204</v>
       </c>
       <c r="D7" t="n">
-        <v>104.322531</v>
+        <v>105.83896</v>
       </c>
     </row>
     <row r="8">
@@ -4024,10 +4024,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
-        <v>54.90161</v>
+        <v>54.646324</v>
       </c>
       <c r="D8" t="n">
-        <v>110.035662</v>
+        <v>109.992822</v>
       </c>
     </row>
     <row r="9">
@@ -4040,10 +4040,10 @@
         <v>205</v>
       </c>
       <c r="C9" t="n">
-        <v>55.116668</v>
+        <v>55.875066</v>
       </c>
       <c r="D9" t="n">
-        <v>112.967699</v>
+        <v>113.726261</v>
       </c>
     </row>
     <row r="10">
@@ -4056,10 +4056,10 @@
         <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>56.453636</v>
+        <v>56.076078</v>
       </c>
       <c r="D10" t="n">
-        <v>105.640664</v>
+        <v>106.199664</v>
       </c>
     </row>
     <row r="11">
@@ -4072,10 +4072,10 @@
         <v>363</v>
       </c>
       <c r="C11" t="n">
-        <v>56.647085</v>
+        <v>56.299987</v>
       </c>
       <c r="D11" t="n">
-        <v>110.582906</v>
+        <v>110.931601</v>
       </c>
     </row>
     <row r="12">
@@ -4088,10 +4088,10 @@
         <v>250</v>
       </c>
       <c r="C12" t="n">
-        <v>56.722249</v>
+        <v>57.703288</v>
       </c>
       <c r="D12" t="n">
-        <v>130.183659</v>
+        <v>131.846468</v>
       </c>
     </row>
     <row r="13">
@@ -4104,10 +4104,10 @@
         <v>237</v>
       </c>
       <c r="C13" t="n">
-        <v>59.752356</v>
+        <v>59.678383</v>
       </c>
       <c r="D13" t="n">
-        <v>132.226525</v>
+        <v>133.201206</v>
       </c>
     </row>
   </sheetData>
@@ -4176,22 +4176,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.514653</v>
+        <v>36.290651</v>
       </c>
       <c r="D2" t="n">
-        <v>69.870515</v>
+        <v>69.5295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58968</v>
+        <v>0.593675</v>
       </c>
       <c r="F2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="G2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
     </row>
     <row r="3">
@@ -4204,22 +4204,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.688228</v>
+        <v>36.672834</v>
       </c>
       <c r="D3" t="n">
-        <v>69.111553</v>
+        <v>68.519842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.598546</v>
+        <v>0.60539</v>
       </c>
       <c r="F3" t="n">
-        <v>36.462146</v>
+        <v>36.281077</v>
       </c>
       <c r="G3" t="n">
-        <v>65.00704899999999</v>
+        <v>64.754706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.57966</v>
+        <v>0.582917</v>
       </c>
     </row>
     <row r="4">
@@ -4232,22 +4232,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.889393</v>
+        <v>35.126332</v>
       </c>
       <c r="D4" t="n">
-        <v>58.967626</v>
+        <v>59.98218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6367969999999999</v>
+        <v>0.624192</v>
       </c>
       <c r="F4" t="n">
-        <v>35.067906</v>
+        <v>35.228584</v>
       </c>
       <c r="G4" t="n">
-        <v>62.838944</v>
+        <v>62.982538</v>
       </c>
       <c r="H4" t="n">
-        <v>0.593066</v>
+        <v>0.591204</v>
       </c>
     </row>
     <row r="5">
@@ -4260,22 +4260,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.094901</v>
+        <v>36.126424</v>
       </c>
       <c r="D5" t="n">
-        <v>60.164585</v>
+        <v>60.383322</v>
       </c>
       <c r="E5" t="n">
-        <v>0.621903</v>
+        <v>0.619148</v>
       </c>
       <c r="F5" t="n">
-        <v>36.37978</v>
+        <v>36.52823</v>
       </c>
       <c r="G5" t="n">
-        <v>63.813279</v>
+        <v>64.110068</v>
       </c>
       <c r="H5" t="n">
-        <v>0.580349</v>
+        <v>0.5764359999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4288,22 +4288,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.408131</v>
+        <v>34.28644</v>
       </c>
       <c r="D6" t="n">
-        <v>56.299874</v>
+        <v>55.38688</v>
       </c>
       <c r="E6" t="n">
-        <v>0.641075</v>
+        <v>0.652621</v>
       </c>
       <c r="F6" t="n">
-        <v>35.791413</v>
+        <v>35.932129</v>
       </c>
       <c r="G6" t="n">
-        <v>65.30998099999999</v>
+        <v>65.073075</v>
       </c>
       <c r="H6" t="n">
-        <v>0.570245</v>
+        <v>0.573358</v>
       </c>
     </row>
     <row r="7">
@@ -4316,22 +4316,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.113191</v>
+        <v>35.382753</v>
       </c>
       <c r="D7" t="n">
-        <v>55.946691</v>
+        <v>56.056533</v>
       </c>
       <c r="E7" t="n">
-        <v>0.645564</v>
+        <v>0.644171</v>
       </c>
       <c r="F7" t="n">
-        <v>36.001267</v>
+        <v>35.863176</v>
       </c>
       <c r="G7" t="n">
-        <v>62.884274</v>
+        <v>63.706891</v>
       </c>
       <c r="H7" t="n">
-        <v>0.601576</v>
+        <v>0.5910840000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.536622</v>
+        <v>35.622593</v>
       </c>
       <c r="D8" t="n">
-        <v>57.36586</v>
+        <v>58.079738</v>
       </c>
       <c r="E8" t="n">
-        <v>0.625829</v>
+        <v>0.616458</v>
       </c>
       <c r="F8" t="n">
-        <v>34.553038</v>
+        <v>34.597901</v>
       </c>
       <c r="G8" t="n">
-        <v>59.014513</v>
+        <v>59.12713</v>
       </c>
       <c r="H8" t="n">
-        <v>0.693093</v>
+        <v>0.691921</v>
       </c>
     </row>
     <row r="9">
@@ -4372,22 +4372,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.912419</v>
+        <v>35.880055</v>
       </c>
       <c r="D9" t="n">
-        <v>57.852448</v>
+        <v>57.399096</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6194539999999999</v>
+        <v>0.625395</v>
       </c>
       <c r="F9" t="n">
-        <v>36.066799</v>
+        <v>35.857649</v>
       </c>
       <c r="G9" t="n">
-        <v>60.2152</v>
+        <v>60.09402</v>
       </c>
       <c r="H9" t="n">
-        <v>0.680478</v>
+        <v>0.681763</v>
       </c>
     </row>
     <row r="10">
@@ -4400,22 +4400,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.629026</v>
+        <v>37.663823</v>
       </c>
       <c r="D10" t="n">
-        <v>70.60959</v>
+        <v>70.664214</v>
       </c>
       <c r="E10" t="n">
-        <v>0.577431</v>
+        <v>0.576777</v>
       </c>
       <c r="F10" t="n">
-        <v>36.193165</v>
+        <v>36.147287</v>
       </c>
       <c r="G10" t="n">
-        <v>67.690298</v>
+        <v>66.696741</v>
       </c>
       <c r="H10" t="n">
-        <v>0.55669</v>
+        <v>0.569608</v>
       </c>
     </row>
     <row r="11">
@@ -4428,22 +4428,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.543552</v>
+        <v>38.464617</v>
       </c>
       <c r="D11" t="n">
-        <v>72.87899899999999</v>
+        <v>72.11625600000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.549831</v>
+        <v>0.559205</v>
       </c>
       <c r="F11" t="n">
-        <v>36.649994</v>
+        <v>36.651831</v>
       </c>
       <c r="G11" t="n">
-        <v>67.74824700000001</v>
+        <v>67.824404</v>
       </c>
       <c r="H11" t="n">
-        <v>0.55593</v>
+        <v>0.554931</v>
       </c>
     </row>
   </sheetData>

--- a/course-design-2/outputs/tables/ch7/49_stage26_3_metrics_after_feature_removal.xlsx
+++ b/course-design-2/outputs/tables/ch7/49_stage26_3_metrics_after_feature_removal.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_特征组维度对照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_三种划分统一协议" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_消融五配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_消融增量bootstrap" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_模型比较" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_最终模型测试集" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_分组预测误差四分位" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_岗位大类预测误差" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_多种子明细" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_多种子汇总" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_公司分组多次划分" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_公司分组汇总" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_稳健性对照" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_主模型SHAP特征" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_技能SHAP" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_特征组维度对照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_三种划分统一协议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_消融五配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_消融增量bootstrap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_模型比较" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_最终模型测试集" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_分组预测误差四分位" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位大类预测误差" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_多种子明细" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_多种子汇总" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司分组多次划分" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_公司分组汇总" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_稳健性对照" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_主模型SHAP特征" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_技能SHAP" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -702,16 +702,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.505337</v>
+        <v>36.470458</v>
       </c>
       <c r="C2" t="n">
-        <v>1.189704</v>
+        <v>1.288387</v>
       </c>
       <c r="D2" t="n">
-        <v>36.236393</v>
+        <v>36.311997</v>
       </c>
       <c r="E2" t="n">
-        <v>0.36827</v>
+        <v>0.272973</v>
       </c>
     </row>
     <row r="3">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.797968</v>
+        <v>35.795565</v>
       </c>
       <c r="C3" t="n">
-        <v>1.273845</v>
+        <v>1.293429</v>
       </c>
       <c r="D3" t="n">
-        <v>35.652079</v>
+        <v>35.611477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.725893</v>
+        <v>0.789422</v>
       </c>
     </row>
   </sheetData>
@@ -814,13 +814,13 @@
         <v>1688</v>
       </c>
       <c r="G2" t="n">
-        <v>51.629921</v>
+        <v>52.093534</v>
       </c>
       <c r="H2" t="n">
-        <v>103.613495</v>
+        <v>103.691486</v>
       </c>
       <c r="I2" t="n">
-        <v>0.135197</v>
+        <v>0.133895</v>
       </c>
     </row>
     <row r="3">
@@ -843,13 +843,13 @@
         <v>2842</v>
       </c>
       <c r="G3" t="n">
-        <v>82.58488</v>
+        <v>82.47614900000001</v>
       </c>
       <c r="H3" t="n">
-        <v>123.1848</v>
+        <v>123.390683</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.008298</v>
+        <v>-0.011671</v>
       </c>
     </row>
     <row r="4">
@@ -872,13 +872,13 @@
         <v>1988</v>
       </c>
       <c r="G4" t="n">
-        <v>38.900334</v>
+        <v>39.044977</v>
       </c>
       <c r="H4" t="n">
-        <v>61.7547</v>
+        <v>62.179762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.156064</v>
+        <v>0.144406</v>
       </c>
     </row>
     <row r="5">
@@ -901,13 +901,13 @@
         <v>1867</v>
       </c>
       <c r="G5" t="n">
-        <v>50.045322</v>
+        <v>49.309929</v>
       </c>
       <c r="H5" t="n">
-        <v>103.444926</v>
+        <v>101.15176</v>
       </c>
       <c r="I5" t="n">
-        <v>0.086599</v>
+        <v>0.126647</v>
       </c>
     </row>
     <row r="6">
@@ -930,13 +930,13 @@
         <v>1870</v>
       </c>
       <c r="G6" t="n">
-        <v>47.035979</v>
+        <v>47.308772</v>
       </c>
       <c r="H6" t="n">
-        <v>80.35033</v>
+        <v>80.328197</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07245699999999999</v>
+        <v>0.07296800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.039287</v>
+        <v>54.046672</v>
       </c>
     </row>
     <row r="3">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.694624</v>
+        <v>16.620295</v>
       </c>
     </row>
     <row r="4">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.900334</v>
+        <v>39.044977</v>
       </c>
     </row>
     <row r="5">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.58488</v>
+        <v>82.47614900000001</v>
       </c>
     </row>
     <row r="6">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94.46965</v>
+        <v>94.14837799999999</v>
       </c>
     </row>
     <row r="7">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.761042</v>
+        <v>23.495853</v>
       </c>
     </row>
     <row r="8">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.088404</v>
+        <v>0.093249</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.063985</v>
+        <v>0.064815</v>
       </c>
     </row>
   </sheetData>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>真实薪资，主统计范围未缩尾</t>
+          <t>真实薪资，主口径未缩尾</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="D2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.626154</v>
+        <v>34.938834</v>
       </c>
       <c r="D3" t="n">
-        <v>67.781775</v>
+        <v>67.93594</v>
       </c>
       <c r="E3" t="n">
-        <v>0.543011</v>
+        <v>0.54093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>目标定义 薪资下限</t>
+          <t>目标口径 薪资下限</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.615346</v>
+        <v>40.609474</v>
       </c>
       <c r="D4" t="n">
-        <v>73.904258</v>
+        <v>73.84469799999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.456726</v>
+        <v>0.457601</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>目标定义 薪资上限</t>
+          <t>目标口径 薪资上限</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48.320296</v>
+        <v>47.608849</v>
       </c>
       <c r="D5" t="n">
-        <v>74.64457</v>
+        <v>74.051376</v>
       </c>
       <c r="E5" t="n">
-        <v>0.445787</v>
+        <v>0.454561</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1206,12 +1206,9 @@
           <t>winsorize 与主模型 gain 排名的 Spearman</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.955780，共有特征 308 个</t>
+          <t>0.958010，共有特征 308 个</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1223,9 @@
           <t>三种随机种子 42、7、2024 与主模型 mean|SHAP| 排名的 Spearman</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.921362；0.883417（共同特征 308 个）</t>
+          <t>0.924430；0.885505（共同特征 308 个）</t>
         </is>
       </c>
     </row>
@@ -1283,16 +1277,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.705638</v>
+        <v>14.650814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.092603</v>
+        <v>0.092483</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>143.303137</v>
+        <v>142.205072</v>
       </c>
     </row>
     <row r="3">
@@ -1302,16 +1296,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.330178</v>
+        <v>7.135123</v>
       </c>
       <c r="C3" t="n">
-        <v>0.046159</v>
+        <v>0.04504</v>
       </c>
       <c r="D3" t="n">
         <v>882</v>
       </c>
       <c r="E3" t="n">
-        <v>7.462976</v>
+        <v>7.761496</v>
       </c>
     </row>
     <row r="4">
@@ -1321,16 +1315,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.177796</v>
+        <v>5.850328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.038902</v>
+        <v>0.03693</v>
       </c>
       <c r="D4" t="n">
         <v>1091</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.444624</v>
+        <v>-5.324489</v>
       </c>
     </row>
     <row r="5">
@@ -1340,16 +1334,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.81999</v>
+        <v>5.477707</v>
       </c>
       <c r="C5" t="n">
-        <v>0.036649</v>
+        <v>0.034578</v>
       </c>
       <c r="D5" t="n">
         <v>2085</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9770219999999999</v>
+        <v>-1.045766</v>
       </c>
     </row>
     <row r="6">
@@ -1359,16 +1353,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.210702</v>
+        <v>4.768654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.032813</v>
+        <v>0.030102</v>
       </c>
       <c r="D6" t="n">
         <v>1374</v>
       </c>
       <c r="E6" t="n">
-        <v>4.299848</v>
+        <v>3.979958</v>
       </c>
     </row>
     <row r="7">
@@ -1378,73 +1372,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.677698</v>
+        <v>4.528253</v>
       </c>
       <c r="C7" t="n">
-        <v>0.029456</v>
+        <v>0.028585</v>
       </c>
       <c r="D7" t="n">
         <v>1539</v>
       </c>
       <c r="E7" t="n">
-        <v>3.572391</v>
+        <v>3.421217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>岗位细分类集合=人工智能</t>
+          <t>文本SVD4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.118153</v>
+        <v>4.043529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.025933</v>
+        <v>0.025525</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>970</v>
       </c>
       <c r="E8" t="n">
-        <v>19.641069</v>
+        <v>4.648573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>文本SVD4</t>
+          <t>学历等级</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.048801</v>
+        <v>3.824677</v>
       </c>
       <c r="C9" t="n">
-        <v>0.025496</v>
+        <v>0.024143</v>
       </c>
       <c r="D9" t="n">
-        <v>969</v>
+        <v>1934</v>
       </c>
       <c r="E9" t="n">
-        <v>4.675362</v>
+        <v>-0.698518</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>学历等级</t>
+          <t>岗位细分类集合=人工智能</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.731974</v>
+        <v>3.80716</v>
       </c>
       <c r="C10" t="n">
-        <v>0.023501</v>
+        <v>0.024033</v>
       </c>
       <c r="D10" t="n">
-        <v>1934</v>
+        <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.693551</v>
+        <v>17.60929</v>
       </c>
     </row>
     <row r="11">
@@ -1454,16 +1448,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.707983</v>
+        <v>3.704116</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02335</v>
+        <v>0.023382</v>
       </c>
       <c r="D11" t="n">
         <v>985</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.297125</v>
+        <v>-3.503971</v>
       </c>
     </row>
     <row r="12">
@@ -1473,16 +1467,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.639079</v>
+        <v>3.63502</v>
       </c>
       <c r="C12" t="n">
-        <v>0.022916</v>
+        <v>0.022946</v>
       </c>
       <c r="D12" t="n">
         <v>1003</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.417148</v>
+        <v>-3.714797</v>
       </c>
     </row>
     <row r="13">
@@ -1492,16 +1486,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.459057</v>
+        <v>3.383803</v>
       </c>
       <c r="C13" t="n">
-        <v>0.021782</v>
+        <v>0.02136</v>
       </c>
       <c r="D13" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.317593</v>
+        <v>-3.143047</v>
       </c>
     </row>
     <row r="14">
@@ -1511,16 +1505,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.945658</v>
+        <v>3.208004</v>
       </c>
       <c r="C14" t="n">
-        <v>0.018549</v>
+        <v>0.020251</v>
       </c>
       <c r="D14" t="n">
         <v>1111</v>
       </c>
       <c r="E14" t="n">
-        <v>2.841705</v>
+        <v>3.14565</v>
       </c>
     </row>
     <row r="15">
@@ -1530,35 +1524,35 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.696593</v>
+        <v>2.612568</v>
       </c>
       <c r="C15" t="n">
-        <v>0.016981</v>
+        <v>0.016492</v>
       </c>
       <c r="D15" t="n">
         <v>149</v>
       </c>
       <c r="E15" t="n">
-        <v>19.806623</v>
+        <v>19.211357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>办公工具技能数</t>
+          <t>公司标签列表=节日礼品</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.390356</v>
+        <v>2.377729</v>
       </c>
       <c r="C16" t="n">
-        <v>0.015052</v>
+        <v>0.015009</v>
       </c>
       <c r="D16" t="n">
-        <v>642</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.933457</v>
+        <v>22.914475</v>
       </c>
     </row>
   </sheetData>
@@ -1615,10 +1609,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>18.895386</v>
+        <v>20.309731</v>
       </c>
       <c r="E2" t="n">
-        <v>1.544092</v>
+        <v>1.595466</v>
       </c>
     </row>
     <row r="3">
@@ -1634,10 +1628,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>37.063207</v>
+        <v>39.450919</v>
       </c>
       <c r="E3" t="n">
-        <v>0.537763</v>
+        <v>0.568829</v>
       </c>
     </row>
     <row r="4">
@@ -1653,10 +1647,10 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.397708</v>
+        <v>-1.252545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.41965</v>
+        <v>0.424138</v>
       </c>
     </row>
     <row r="5">
@@ -1672,29 +1666,29 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4638</v>
+        <v>5.613044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.323876</v>
+        <v>0.410317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>办公软件</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2591</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>361</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.642235</v>
+        <v>6.378203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.287768</v>
+        <v>0.298474</v>
       </c>
     </row>
     <row r="7">
@@ -1710,390 +1704,390 @@
         <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.684283</v>
+        <v>-0.605727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.238274</v>
+        <v>0.287314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>办公软件</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>419</v>
+        <v>2591</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>361</v>
       </c>
       <c r="D8" t="n">
-        <v>4.596505</v>
+        <v>-0.602569</v>
       </c>
       <c r="E8" t="n">
-        <v>0.23797</v>
+        <v>0.27834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>项目管理</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>487</v>
+        <v>619</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>3.630267</v>
+        <v>-2.802243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.218202</v>
+        <v>0.244993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>深度学习</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.119757</v>
+        <v>0.185444</v>
       </c>
       <c r="E10" t="n">
-        <v>0.217002</v>
+        <v>0.192438</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>7.378255</v>
+        <v>5.033364</v>
       </c>
       <c r="E11" t="n">
-        <v>0.159323</v>
+        <v>0.169483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>深度学习</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>572</v>
+        <v>179</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.460794</v>
+        <v>9.070301000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.152885</v>
+        <v>0.164902</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>项目管理</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>231</v>
+        <v>487</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>2.401782</v>
+        <v>2.375569</v>
       </c>
       <c r="E13" t="n">
-        <v>0.131006</v>
+        <v>0.145479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>3.160007</v>
+        <v>1.59028</v>
       </c>
       <c r="E14" t="n">
-        <v>0.120394</v>
+        <v>0.119964</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>大数据</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.316639</v>
+        <v>3.390473</v>
       </c>
       <c r="E15" t="n">
-        <v>0.104936</v>
+        <v>0.092444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>238</v>
+        <v>446</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>3.352356</v>
+        <v>1.443804</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09164899999999999</v>
+        <v>0.088058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prompt Engineering</t>
+          <t>大模型</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>202</v>
+        <v>866</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.165765</v>
+        <v>0.585784</v>
       </c>
       <c r="E17" t="n">
-        <v>0.087244</v>
+        <v>0.07851900000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>大模型</t>
+          <t>Prompt Engineering</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>866</v>
+        <v>202</v>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>0.575404</v>
+        <v>-2.744291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08491</v>
+        <v>0.07831100000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>产品设计</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="C19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" t="n">
-        <v>1.126344</v>
+        <v>0.862005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.074971</v>
+        <v>0.061806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>原型设计</t>
+          <t>MATLAB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>445</v>
+        <v>118</v>
       </c>
       <c r="C20" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>1.385965</v>
+        <v>4.565779</v>
       </c>
       <c r="E20" t="n">
-        <v>0.068438</v>
+        <v>0.061594</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MATLAB</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>3.621004</v>
+        <v>4.564088</v>
       </c>
       <c r="E21" t="n">
-        <v>0.051461</v>
+        <v>0.055087</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>原型设计</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>205</v>
+        <v>445</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="D22" t="n">
-        <v>2.201653</v>
+        <v>1.192743</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04988</v>
+        <v>0.052803</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>3.145494</v>
+        <v>2.283927</v>
       </c>
       <c r="E23" t="n">
-        <v>0.049464</v>
+        <v>0.052133</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TensorFlow</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.244522</v>
+        <v>1.702743</v>
       </c>
       <c r="E24" t="n">
-        <v>0.047529</v>
+        <v>0.050848</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>TensorFlow</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2418</v>
+        <v>277</v>
       </c>
       <c r="C25" t="n">
-        <v>374</v>
+        <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.093982</v>
+        <v>-1.610609</v>
       </c>
       <c r="E25" t="n">
-        <v>0.045385</v>
+        <v>0.049511</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>大数据</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D26" t="n">
-        <v>1.338755</v>
+        <v>-1.086094</v>
       </c>
       <c r="E26" t="n">
-        <v>0.041555</v>
+        <v>0.042894</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>前端</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="C27" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.961083</v>
+        <v>1.693931</v>
       </c>
       <c r="E27" t="n">
-        <v>0.038997</v>
+        <v>0.041898</v>
       </c>
     </row>
     <row r="28">
@@ -2109,422 +2103,422 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>1.955409</v>
+        <v>1.960333</v>
       </c>
       <c r="E28" t="n">
-        <v>0.036787</v>
+        <v>0.038642</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>市场调研</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1387</v>
+        <v>437</v>
       </c>
       <c r="C29" t="n">
-        <v>208</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>0.176623</v>
+        <v>-0.646269</v>
       </c>
       <c r="E29" t="n">
-        <v>0.035982</v>
+        <v>0.034002</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>市场调研</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>437</v>
+        <v>210</v>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6566689999999999</v>
+        <v>-0.512134</v>
       </c>
       <c r="E30" t="n">
-        <v>0.035161</v>
+        <v>0.033688</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>AIGC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D31" t="n">
-        <v>1.199815</v>
+        <v>-0.354326</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03402</v>
+        <v>0.031923</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>微调</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.797368</v>
+        <v>2.080506</v>
       </c>
       <c r="E32" t="n">
-        <v>0.032409</v>
+        <v>0.026504</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>数据挖掘</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>156</v>
+        <v>2418</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>374</v>
       </c>
       <c r="D33" t="n">
-        <v>1.78618</v>
+        <v>-0.027427</v>
       </c>
       <c r="E33" t="n">
-        <v>0.031935</v>
+        <v>0.026144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AIGC</t>
+          <t>PyTorch</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="C34" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.584211</v>
+        <v>-0.11973</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03045</v>
+        <v>0.016814</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PyTorch</t>
+          <t>PPT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>394</v>
+        <v>1341</v>
       </c>
       <c r="C35" t="n">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.377143</v>
+        <v>0.064017</v>
       </c>
       <c r="E35" t="n">
-        <v>0.026096</v>
+        <v>0.015952</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2737</v>
+        <v>152</v>
       </c>
       <c r="C36" t="n">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>0.078431</v>
+        <v>0.445503</v>
       </c>
       <c r="E36" t="n">
-        <v>0.02578</v>
+        <v>0.015238</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>产品设计</t>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>484</v>
+        <v>156</v>
       </c>
       <c r="C37" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>0.355223</v>
+        <v>0.41228</v>
       </c>
       <c r="E37" t="n">
-        <v>0.025218</v>
+        <v>0.014415</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>152</v>
+        <v>266</v>
       </c>
       <c r="C38" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D38" t="n">
-        <v>0.913724</v>
+        <v>0.03734</v>
       </c>
       <c r="E38" t="n">
-        <v>0.024421</v>
+        <v>0.014397</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>210</v>
+        <v>2737</v>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>426</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.888567</v>
+        <v>0.018826</v>
       </c>
       <c r="E39" t="n">
-        <v>0.022363</v>
+        <v>0.013646</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>用户研究</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>383</v>
+        <v>1387</v>
       </c>
       <c r="C40" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="D40" t="n">
-        <v>0.351346</v>
+        <v>0.04891</v>
       </c>
       <c r="E40" t="n">
-        <v>0.019387</v>
+        <v>0.012991</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>微调</t>
+          <t>数据可视化</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>132</v>
+        <v>409</v>
       </c>
       <c r="C41" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9882339999999999</v>
+        <v>0.240141</v>
       </c>
       <c r="E41" t="n">
-        <v>0.013472</v>
+        <v>0.012701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PPT</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1341</v>
+        <v>110</v>
       </c>
       <c r="C42" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>0.056657</v>
+        <v>-0.953856</v>
       </c>
       <c r="E42" t="n">
-        <v>0.011213</v>
+        <v>0.011953</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>内容运营</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>774</v>
+        <v>140</v>
       </c>
       <c r="C43" t="n">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="D43" t="n">
-        <v>0.091862</v>
+        <v>-0.693805</v>
       </c>
       <c r="E43" t="n">
-        <v>0.009009</v>
+        <v>0.010172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>后端</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>235</v>
+        <v>599</v>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D44" t="n">
-        <v>0.155069</v>
+        <v>0.107375</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006662</v>
+        <v>0.009016</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>数据运营</t>
+          <t>用户研究</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>146</v>
+        <v>383</v>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="D45" t="n">
-        <v>0.330738</v>
+        <v>0.114805</v>
       </c>
       <c r="E45" t="n">
-        <v>0.006451</v>
+        <v>0.008917</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.100169</v>
+        <v>-0.598542</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004119</v>
+        <v>0.007638</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>后端</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
-        <v>0.08774800000000001</v>
+        <v>0.124843</v>
       </c>
       <c r="E47" t="n">
-        <v>0.002464</v>
+        <v>0.006802</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>内容运营</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>143</v>
+        <v>774</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.050326</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.005214</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>单元测试</t>
+          <t>React</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>-0.309497</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.004452</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>599</v>
+        <v>165</v>
       </c>
       <c r="C50" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2536,14 +2530,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>单元测试</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2555,14 +2549,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>数据可视化</t>
+          <t>数据运营</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>409</v>
+        <v>146</v>
       </c>
       <c r="C52" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2669,22 +2663,22 @@
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="H2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
       <c r="J2" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="K2" t="n">
-        <v>69.5295</v>
+        <v>69.870515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.593675</v>
+        <v>0.58968</v>
       </c>
     </row>
     <row r="3">
@@ -2709,22 +2703,22 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>51.629921</v>
+        <v>52.093534</v>
       </c>
       <c r="H3" t="n">
-        <v>103.613495</v>
+        <v>103.691486</v>
       </c>
       <c r="I3" t="n">
-        <v>0.135197</v>
+        <v>0.133895</v>
       </c>
       <c r="J3" t="n">
-        <v>56.91992</v>
+        <v>56.83264</v>
       </c>
       <c r="K3" t="n">
-        <v>99.77120600000001</v>
+        <v>99.962637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.145423</v>
+        <v>0.14214</v>
       </c>
     </row>
     <row r="4">
@@ -2749,22 +2743,22 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>31.858455</v>
+        <v>32.132572</v>
       </c>
       <c r="H4" t="n">
-        <v>48.03658</v>
+        <v>47.817303</v>
       </c>
       <c r="I4" t="n">
-        <v>0.650209</v>
+        <v>0.6533949999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>38.79574</v>
+        <v>39.289746</v>
       </c>
       <c r="K4" t="n">
-        <v>71.836651</v>
+        <v>72.738175</v>
       </c>
       <c r="L4" t="n">
-        <v>0.515406</v>
+        <v>0.503167</v>
       </c>
     </row>
   </sheetData>
@@ -2942,22 +2936,22 @@
         <v>246</v>
       </c>
       <c r="D4" t="n">
-        <v>36.596275</v>
+        <v>36.684903</v>
       </c>
       <c r="E4" t="n">
-        <v>71.288178</v>
+        <v>70.934708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.57286</v>
+        <v>0.577086</v>
       </c>
       <c r="G4" t="n">
-        <v>36.490756</v>
+        <v>36.163106</v>
       </c>
       <c r="H4" t="n">
-        <v>66.761292</v>
+        <v>66.26462600000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5566680000000001</v>
+        <v>0.563239</v>
       </c>
       <c r="J4" t="n">
         <v>10418</v>
@@ -2984,22 +2978,22 @@
         <v>308</v>
       </c>
       <c r="D5" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="E5" t="n">
-        <v>69.5295</v>
+        <v>69.870515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.593675</v>
+        <v>0.58968</v>
       </c>
       <c r="G5" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="H5" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
       <c r="J5" t="n">
         <v>10418</v>
@@ -3026,22 +3020,22 @@
         <v>310</v>
       </c>
       <c r="D6" t="n">
-        <v>36.437977</v>
+        <v>36.447279</v>
       </c>
       <c r="E6" t="n">
-        <v>69.80105399999999</v>
+        <v>69.70617799999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.590495</v>
+        <v>0.591608</v>
       </c>
       <c r="G6" t="n">
-        <v>36.4177</v>
+        <v>36.310077</v>
       </c>
       <c r="H6" t="n">
-        <v>67.38436900000001</v>
+        <v>66.51470999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.548354</v>
+        <v>0.559936</v>
       </c>
       <c r="J6" t="n">
         <v>10418</v>
@@ -3131,19 +3125,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="E2" t="n">
-        <v>36.437977</v>
+        <v>36.447279</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.147325</v>
+        <v>0.067375</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.573821</v>
+        <v>-0.419282</v>
       </c>
       <c r="H2" t="n">
-        <v>0.361492</v>
+        <v>0.5450469999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3168,19 +3162,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="E3" t="n">
-        <v>36.4177</v>
+        <v>36.310077</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.063206</v>
+        <v>0.141786</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.497289</v>
+        <v>-0.313526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.352418</v>
+        <v>0.587892</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3282,16 +3276,16 @@
         <v>36.553562</v>
       </c>
       <c r="E6" t="n">
-        <v>36.596275</v>
+        <v>36.684903</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.042713</v>
+        <v>-0.131341</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.26168</v>
+        <v>-1.254886</v>
       </c>
       <c r="H6" t="n">
-        <v>1.099438</v>
+        <v>1.029385</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3319,16 +3313,16 @@
         <v>34.867155</v>
       </c>
       <c r="E7" t="n">
-        <v>36.490756</v>
+        <v>36.163106</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.623601</v>
+        <v>-1.295952</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.711675</v>
+        <v>-2.427373</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.55621</v>
+        <v>-0.264999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3356,16 +3350,16 @@
         <v>36.553562</v>
       </c>
       <c r="E8" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="F8" t="n">
-        <v>0.262911</v>
+        <v>0.038909</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.953264</v>
+        <v>-1.241114</v>
       </c>
       <c r="H8" t="n">
-        <v>1.581866</v>
+        <v>1.323666</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3393,16 +3387,16 @@
         <v>34.867155</v>
       </c>
       <c r="E9" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.487339</v>
+        <v>-1.584708</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.61116</v>
+        <v>-2.711612</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.374832</v>
+        <v>-0.461833</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3478,22 +3472,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="D2" t="n">
-        <v>69.5295</v>
+        <v>69.870515</v>
       </c>
       <c r="E2" t="n">
-        <v>0.593675</v>
+        <v>0.58968</v>
       </c>
       <c r="F2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="G2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
     </row>
     <row r="3">
@@ -3508,22 +3502,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.672834</v>
+        <v>36.688228</v>
       </c>
       <c r="D3" t="n">
-        <v>68.519842</v>
+        <v>69.111553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60539</v>
+        <v>0.598546</v>
       </c>
       <c r="F3" t="n">
-        <v>36.281077</v>
+        <v>36.462146</v>
       </c>
       <c r="G3" t="n">
-        <v>64.754706</v>
+        <v>65.00704899999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.582917</v>
+        <v>0.57966</v>
       </c>
     </row>
     <row r="4">
@@ -3538,22 +3532,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.973974</v>
+        <v>38.221277</v>
       </c>
       <c r="D4" t="n">
-        <v>73.779841</v>
+        <v>74.38752700000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.54248</v>
+        <v>0.5349120000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>36.918553</v>
+        <v>37.045813</v>
       </c>
       <c r="G4" t="n">
-        <v>69.247167</v>
+        <v>68.81978100000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.523038</v>
+        <v>0.528907</v>
       </c>
     </row>
     <row r="5">
@@ -3568,22 +3562,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.314378</v>
+        <v>45.315019</v>
       </c>
       <c r="D5" t="n">
-        <v>85.582283</v>
+        <v>85.583927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.384394</v>
+        <v>0.384371</v>
       </c>
       <c r="F5" t="n">
-        <v>43.674895</v>
+        <v>43.673798</v>
       </c>
       <c r="G5" t="n">
-        <v>77.24099</v>
+        <v>77.239881</v>
       </c>
       <c r="H5" t="n">
-        <v>0.406562</v>
+        <v>0.406579</v>
       </c>
     </row>
     <row r="6">
@@ -3699,13 +3693,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="C2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -3721,13 +3715,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.109171</v>
+        <v>35.28104</v>
       </c>
       <c r="C3" t="n">
-        <v>64.616632</v>
+        <v>64.783455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.584694</v>
+        <v>0.582546</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -3792,10 +3786,10 @@
         <v>2233</v>
       </c>
       <c r="D2" t="n">
-        <v>35.109171</v>
+        <v>35.28104</v>
       </c>
       <c r="E2" t="n">
-        <v>64.616632</v>
+        <v>64.783455</v>
       </c>
     </row>
     <row r="3">
@@ -3813,10 +3807,10 @@
         <v>628</v>
       </c>
       <c r="D3" t="n">
-        <v>35.821356</v>
+        <v>35.434828</v>
       </c>
       <c r="E3" t="n">
-        <v>49.961485</v>
+        <v>48.986959</v>
       </c>
     </row>
     <row r="4">
@@ -3834,10 +3828,10 @@
         <v>702</v>
       </c>
       <c r="D4" t="n">
-        <v>22.326196</v>
+        <v>22.679834</v>
       </c>
       <c r="E4" t="n">
-        <v>30.765701</v>
+        <v>32.165038</v>
       </c>
     </row>
     <row r="5">
@@ -3855,10 +3849,10 @@
         <v>477</v>
       </c>
       <c r="D5" t="n">
-        <v>28.93682</v>
+        <v>29.330488</v>
       </c>
       <c r="E5" t="n">
-        <v>39.968253</v>
+        <v>40.764663</v>
       </c>
     </row>
     <row r="6">
@@ -3876,10 +3870,10 @@
         <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>62.035479</v>
+        <v>62.482639</v>
       </c>
       <c r="E6" t="n">
-        <v>121.892655</v>
+        <v>122.049236</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3922,10 @@
         <v>933</v>
       </c>
       <c r="C2" t="n">
-        <v>29.396959</v>
+        <v>29.295129</v>
       </c>
       <c r="D2" t="n">
-        <v>43.730844</v>
+        <v>43.609982</v>
       </c>
     </row>
     <row r="3">
@@ -3944,58 +3938,58 @@
         <v>1493</v>
       </c>
       <c r="C3" t="n">
-        <v>29.39985</v>
+        <v>29.502945</v>
       </c>
       <c r="D3" t="n">
-        <v>43.294897</v>
+        <v>43.547086</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>技术管理</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C4" t="n">
-        <v>32.971489</v>
+        <v>31.943268</v>
       </c>
       <c r="D4" t="n">
-        <v>44.98865</v>
+        <v>41.119023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>客服</t>
+          <t>技术管理</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="C5" t="n">
-        <v>33.069425</v>
+        <v>32.274806</v>
       </c>
       <c r="D5" t="n">
-        <v>58.25892</v>
+        <v>45.22604</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>客服</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>33.269944</v>
+        <v>33.447434</v>
       </c>
       <c r="D6" t="n">
-        <v>43.399957</v>
+        <v>58.779362</v>
       </c>
     </row>
     <row r="7">
@@ -4008,10 +4002,10 @@
         <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>48.949204</v>
+        <v>48.667314</v>
       </c>
       <c r="D7" t="n">
-        <v>105.83896</v>
+        <v>104.322531</v>
       </c>
     </row>
     <row r="8">
@@ -4024,10 +4018,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
-        <v>54.646324</v>
+        <v>54.90161</v>
       </c>
       <c r="D8" t="n">
-        <v>109.992822</v>
+        <v>110.035662</v>
       </c>
     </row>
     <row r="9">
@@ -4040,10 +4034,10 @@
         <v>205</v>
       </c>
       <c r="C9" t="n">
-        <v>55.875066</v>
+        <v>55.116668</v>
       </c>
       <c r="D9" t="n">
-        <v>113.726261</v>
+        <v>112.967699</v>
       </c>
     </row>
     <row r="10">
@@ -4056,10 +4050,10 @@
         <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>56.076078</v>
+        <v>56.453636</v>
       </c>
       <c r="D10" t="n">
-        <v>106.199664</v>
+        <v>105.640664</v>
       </c>
     </row>
     <row r="11">
@@ -4072,10 +4066,10 @@
         <v>363</v>
       </c>
       <c r="C11" t="n">
-        <v>56.299987</v>
+        <v>56.647085</v>
       </c>
       <c r="D11" t="n">
-        <v>110.931601</v>
+        <v>110.582906</v>
       </c>
     </row>
     <row r="12">
@@ -4088,10 +4082,10 @@
         <v>250</v>
       </c>
       <c r="C12" t="n">
-        <v>57.703288</v>
+        <v>56.722249</v>
       </c>
       <c r="D12" t="n">
-        <v>131.846468</v>
+        <v>130.183659</v>
       </c>
     </row>
     <row r="13">
@@ -4104,10 +4098,10 @@
         <v>237</v>
       </c>
       <c r="C13" t="n">
-        <v>59.678383</v>
+        <v>59.752356</v>
       </c>
       <c r="D13" t="n">
-        <v>133.201206</v>
+        <v>132.226525</v>
       </c>
     </row>
   </sheetData>
@@ -4176,22 +4170,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.290651</v>
+        <v>36.514653</v>
       </c>
       <c r="D2" t="n">
-        <v>69.5295</v>
+        <v>69.870515</v>
       </c>
       <c r="E2" t="n">
-        <v>0.593675</v>
+        <v>0.58968</v>
       </c>
       <c r="F2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="G2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
     </row>
     <row r="3">
@@ -4204,22 +4198,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.672834</v>
+        <v>36.688228</v>
       </c>
       <c r="D3" t="n">
-        <v>68.519842</v>
+        <v>69.111553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60539</v>
+        <v>0.598546</v>
       </c>
       <c r="F3" t="n">
-        <v>36.281077</v>
+        <v>36.462146</v>
       </c>
       <c r="G3" t="n">
-        <v>64.754706</v>
+        <v>65.00704899999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.582917</v>
+        <v>0.57966</v>
       </c>
     </row>
     <row r="4">
@@ -4232,22 +4226,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.126332</v>
+        <v>34.889393</v>
       </c>
       <c r="D4" t="n">
-        <v>59.98218</v>
+        <v>58.967626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.624192</v>
+        <v>0.6367969999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>35.228584</v>
+        <v>35.067906</v>
       </c>
       <c r="G4" t="n">
-        <v>62.982538</v>
+        <v>62.838944</v>
       </c>
       <c r="H4" t="n">
-        <v>0.591204</v>
+        <v>0.593066</v>
       </c>
     </row>
     <row r="5">
@@ -4260,22 +4254,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.126424</v>
+        <v>36.094901</v>
       </c>
       <c r="D5" t="n">
-        <v>60.383322</v>
+        <v>60.164585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.619148</v>
+        <v>0.621903</v>
       </c>
       <c r="F5" t="n">
-        <v>36.52823</v>
+        <v>36.37978</v>
       </c>
       <c r="G5" t="n">
-        <v>64.110068</v>
+        <v>63.813279</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5764359999999999</v>
+        <v>0.580349</v>
       </c>
     </row>
     <row r="6">
@@ -4288,22 +4282,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.28644</v>
+        <v>34.408131</v>
       </c>
       <c r="D6" t="n">
-        <v>55.38688</v>
+        <v>56.299874</v>
       </c>
       <c r="E6" t="n">
-        <v>0.652621</v>
+        <v>0.641075</v>
       </c>
       <c r="F6" t="n">
-        <v>35.932129</v>
+        <v>35.791413</v>
       </c>
       <c r="G6" t="n">
-        <v>65.073075</v>
+        <v>65.30998099999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.573358</v>
+        <v>0.570245</v>
       </c>
     </row>
     <row r="7">
@@ -4316,22 +4310,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.382753</v>
+        <v>35.113191</v>
       </c>
       <c r="D7" t="n">
-        <v>56.056533</v>
+        <v>55.946691</v>
       </c>
       <c r="E7" t="n">
-        <v>0.644171</v>
+        <v>0.645564</v>
       </c>
       <c r="F7" t="n">
-        <v>35.863176</v>
+        <v>36.001267</v>
       </c>
       <c r="G7" t="n">
-        <v>63.706891</v>
+        <v>62.884274</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5910840000000001</v>
+        <v>0.601576</v>
       </c>
     </row>
     <row r="8">
@@ -4344,22 +4338,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.622593</v>
+        <v>35.536622</v>
       </c>
       <c r="D8" t="n">
-        <v>58.079738</v>
+        <v>57.36586</v>
       </c>
       <c r="E8" t="n">
-        <v>0.616458</v>
+        <v>0.625829</v>
       </c>
       <c r="F8" t="n">
-        <v>34.597901</v>
+        <v>34.553038</v>
       </c>
       <c r="G8" t="n">
-        <v>59.12713</v>
+        <v>59.014513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.691921</v>
+        <v>0.693093</v>
       </c>
     </row>
     <row r="9">
@@ -4372,22 +4366,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.880055</v>
+        <v>35.912419</v>
       </c>
       <c r="D9" t="n">
-        <v>57.399096</v>
+        <v>57.852448</v>
       </c>
       <c r="E9" t="n">
-        <v>0.625395</v>
+        <v>0.6194539999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>35.857649</v>
+        <v>36.066799</v>
       </c>
       <c r="G9" t="n">
-        <v>60.09402</v>
+        <v>60.2152</v>
       </c>
       <c r="H9" t="n">
-        <v>0.681763</v>
+        <v>0.680478</v>
       </c>
     </row>
     <row r="10">
@@ -4400,22 +4394,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.663823</v>
+        <v>37.629026</v>
       </c>
       <c r="D10" t="n">
-        <v>70.664214</v>
+        <v>70.60959</v>
       </c>
       <c r="E10" t="n">
-        <v>0.576777</v>
+        <v>0.577431</v>
       </c>
       <c r="F10" t="n">
-        <v>36.147287</v>
+        <v>36.193165</v>
       </c>
       <c r="G10" t="n">
-        <v>66.696741</v>
+        <v>67.690298</v>
       </c>
       <c r="H10" t="n">
-        <v>0.569608</v>
+        <v>0.55669</v>
       </c>
     </row>
     <row r="11">
@@ -4428,22 +4422,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.464617</v>
+        <v>38.543552</v>
       </c>
       <c r="D11" t="n">
-        <v>72.11625600000001</v>
+        <v>72.87899899999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.559205</v>
+        <v>0.549831</v>
       </c>
       <c r="F11" t="n">
-        <v>36.651831</v>
+        <v>36.649994</v>
       </c>
       <c r="G11" t="n">
-        <v>67.824404</v>
+        <v>67.74824700000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.554931</v>
+        <v>0.55593</v>
       </c>
     </row>
   </sheetData>
